--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.05912224547933</v>
+        <v>8.459607364890392</v>
       </c>
       <c r="D2" t="n">
-        <v>52.54594211869395</v>
+        <v>8.538715594287767</v>
       </c>
       <c r="E2" t="n">
-        <v>15.86506611006383</v>
+        <v>2.578073242885373</v>
       </c>
       <c r="F2" t="n">
-        <v>16.35307219702213</v>
+        <v>2.657374232016096</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.44880831019852</v>
+        <v>4.29793135040726</v>
       </c>
       <c r="D3" t="n">
-        <v>31.39777290781317</v>
+        <v>5.10213809751964</v>
       </c>
       <c r="E3" t="n">
-        <v>15.86506611006383</v>
+        <v>2.578073242885373</v>
       </c>
       <c r="F3" t="n">
-        <v>16.35307219702213</v>
+        <v>2.657374232016096</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.547828516847275</v>
+        <v>1.551522133987682</v>
       </c>
       <c r="D4" t="n">
-        <v>9.583070926956569</v>
+        <v>1.557249025630443</v>
       </c>
       <c r="E4" t="n">
-        <v>15.86506611006383</v>
+        <v>2.578073242885373</v>
       </c>
       <c r="F4" t="n">
-        <v>16.35307219702213</v>
+        <v>2.657374232016096</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>18.36379519614969</v>
+        <v>2.984116719374324</v>
       </c>
       <c r="D5" t="n">
-        <v>17.18923594959288</v>
+        <v>2.793250841808843</v>
       </c>
       <c r="E5" t="n">
-        <v>15.86506611006383</v>
+        <v>2.578073242885373</v>
       </c>
       <c r="F5" t="n">
-        <v>16.35307219702213</v>
+        <v>2.657374232016096</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
